--- a/data/paper_data.xlsx
+++ b/data/paper_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Dell2/Desktop/housing-monetary-policy-turkiye/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1388EEEE-EF99-AA45-9A95-BA5E0C6D6B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6D056A-7E9D-E34B-A247-195267A88A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17400" activeTab="1" xr2:uid="{FF058481-EF7F-684B-B604-B6CAD0081A0C}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17400" xr2:uid="{FF058481-EF7F-684B-B604-B6CAD0081A0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Prepared Data for Regression" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="128">
   <si>
     <t/>
   </si>
@@ -277,9 +277,6 @@
   </si>
   <si>
     <t>gold_mth_gwt_rate</t>
-  </si>
-  <si>
-    <t>mp_surp</t>
   </si>
   <si>
     <t>Date</t>
@@ -848,13 +845,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E4664A-7313-E949-8398-58544CEB8A31}">
-  <dimension ref="A1:CB161"/>
+  <dimension ref="A1:CA161"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1092,11 +1089,8 @@
       <c r="CA1" t="s">
         <v>79</v>
       </c>
-      <c r="CB1" t="s">
-        <v>80</v>
-      </c>
     </row>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>41275</v>
       </c>
@@ -1259,11 +1253,8 @@
       <c r="CA2">
         <v>-7.8607724789465649E-3</v>
       </c>
-      <c r="CB2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>41306</v>
       </c>
@@ -1438,11 +1429,8 @@
       <c r="CA3">
         <v>-1.9537120529005136E-2</v>
       </c>
-      <c r="CB3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>41334</v>
       </c>
@@ -1617,11 +1605,8 @@
       <c r="CA4">
         <v>-2.3237277743715534E-2</v>
       </c>
-      <c r="CB4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>41365</v>
       </c>
@@ -1796,11 +1781,8 @@
       <c r="CA5">
         <v>-6.1502730525390792E-2</v>
       </c>
-      <c r="CB5">
-        <v>-0.25</v>
-      </c>
     </row>
-    <row r="6" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>41395</v>
       </c>
@@ -1975,11 +1957,8 @@
       <c r="CA6">
         <v>-5.7032211461287341E-2</v>
       </c>
-      <c r="CB6">
-        <v>-0.25</v>
-      </c>
     </row>
-    <row r="7" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>41426</v>
       </c>
@@ -2154,11 +2133,8 @@
       <c r="CA7">
         <v>-6.6482249884739497E-2</v>
       </c>
-      <c r="CB7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>41456</v>
       </c>
@@ -2333,11 +2309,8 @@
       <c r="CA8">
         <v>-2.7588669726164694E-2</v>
       </c>
-      <c r="CB8">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>41487</v>
       </c>
@@ -2512,11 +2485,8 @@
       <c r="CA9">
         <v>4.2435986591759622E-2</v>
       </c>
-      <c r="CB9">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>41518</v>
       </c>
@@ -2691,11 +2661,8 @@
       <c r="CA10">
         <v>1.1100950439240975E-2</v>
       </c>
-      <c r="CB10">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>41548</v>
       </c>
@@ -2870,11 +2837,8 @@
       <c r="CA11">
         <v>-3.0594619439111015E-2</v>
       </c>
-      <c r="CB11">
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>41579</v>
       </c>
@@ -3049,11 +3013,8 @@
       <c r="CA12">
         <v>-2.4402367587905149E-2</v>
       </c>
-      <c r="CB12">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>41609</v>
       </c>
@@ -3228,11 +3189,8 @@
       <c r="CA13">
         <v>-4.4671761708798718E-2</v>
       </c>
-      <c r="CB13">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>41640</v>
       </c>
@@ -3407,11 +3365,8 @@
       <c r="CA14">
         <v>2.5099281236666604E-2</v>
       </c>
-      <c r="CB14">
-        <v>5.5</v>
-      </c>
     </row>
-    <row r="15" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>41671</v>
       </c>
@@ -3586,11 +3541,8 @@
       <c r="CA15">
         <v>4.6344098931444533E-2</v>
       </c>
-      <c r="CB15">
-        <v>0</v>
-      </c>
     </row>
-    <row r="16" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>41699</v>
       </c>
@@ -3765,11 +3717,8 @@
       <c r="CA16">
         <v>2.3331420921782309E-2</v>
       </c>
-      <c r="CB16">
-        <v>0</v>
-      </c>
     </row>
-    <row r="17" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>41730</v>
       </c>
@@ -3944,11 +3893,8 @@
       <c r="CA17">
         <v>-2.5326107269669329E-2</v>
       </c>
-      <c r="CB17">
-        <v>0</v>
-      </c>
     </row>
-    <row r="18" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>41760</v>
       </c>
@@ -4123,11 +4069,8 @@
       <c r="CA18">
         <v>-1.7386702662075093E-2</v>
       </c>
-      <c r="CB18">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="19" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>41791</v>
       </c>
@@ -4302,11 +4245,8 @@
       <c r="CA19">
         <v>5.0109272556977391E-3</v>
       </c>
-      <c r="CB19">
-        <v>-0.25</v>
-      </c>
     </row>
-    <row r="20" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>41821</v>
       </c>
@@ -4481,11 +4421,8 @@
       <c r="CA20">
         <v>2.0534008480763033E-2</v>
       </c>
-      <c r="CB20">
-        <v>0</v>
-      </c>
     </row>
-    <row r="21" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>41852</v>
       </c>
@@ -4660,11 +4597,8 @@
       <c r="CA21">
         <v>-1.6787665707806321E-2</v>
       </c>
-      <c r="CB21">
-        <v>0</v>
-      </c>
     </row>
-    <row r="22" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>41883</v>
       </c>
@@ -4839,11 +4773,8 @@
       <c r="CA22">
         <v>-4.5859133126935014E-2</v>
       </c>
-      <c r="CB22">
-        <v>0</v>
-      </c>
     </row>
-    <row r="23" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>41913</v>
       </c>
@@ -5018,11 +4949,8 @@
       <c r="CA23">
         <v>-1.9225309267897006E-2</v>
       </c>
-      <c r="CB23">
-        <v>0</v>
-      </c>
     </row>
-    <row r="24" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>41944</v>
       </c>
@@ -5197,11 +5125,8 @@
       <c r="CA24">
         <v>-2.6094867871469307E-2</v>
       </c>
-      <c r="CB24">
-        <v>0</v>
-      </c>
     </row>
-    <row r="25" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>41974</v>
       </c>
@@ -5379,11 +5304,8 @@
       <c r="CA25">
         <v>1.5337579617834329E-2</v>
       </c>
-      <c r="CB25">
-        <v>0</v>
-      </c>
     </row>
-    <row r="26" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>42005</v>
       </c>
@@ -5561,11 +5483,8 @@
       <c r="CA26">
         <v>4.0892970658101824E-2</v>
       </c>
-      <c r="CB26">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="27" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>42036</v>
       </c>
@@ -5743,11 +5662,8 @@
       <c r="CA27">
         <v>-1.6489212101731709E-2</v>
       </c>
-      <c r="CB27">
-        <v>0</v>
-      </c>
     </row>
-    <row r="28" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>42064</v>
       </c>
@@ -5925,11 +5841,8 @@
       <c r="CA28">
         <v>-3.862966019298486E-2</v>
       </c>
-      <c r="CB28">
-        <v>0</v>
-      </c>
     </row>
-    <row r="29" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>42095</v>
       </c>
@@ -6107,11 +6020,8 @@
       <c r="CA29">
         <v>1.8187226447966554E-2</v>
       </c>
-      <c r="CB29">
-        <v>0</v>
-      </c>
     </row>
-    <row r="30" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>42125</v>
       </c>
@@ -6289,11 +6199,8 @@
       <c r="CA30">
         <v>1.285422144317927E-3</v>
       </c>
-      <c r="CB30">
-        <v>0</v>
-      </c>
     </row>
-    <row r="31" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>42156</v>
       </c>
@@ -6471,11 +6378,8 @@
       <c r="CA31">
         <v>-1.6063821805783585E-2</v>
       </c>
-      <c r="CB31">
-        <v>0</v>
-      </c>
     </row>
-    <row r="32" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>42186</v>
       </c>
@@ -6653,11 +6557,8 @@
       <c r="CA32">
         <v>-4.4454046360309141E-2</v>
       </c>
-      <c r="CB32">
-        <v>0</v>
-      </c>
     </row>
-    <row r="33" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>42217</v>
       </c>
@@ -6835,11 +6736,8 @@
       <c r="CA33">
         <v>-6.3128962184686443E-3</v>
       </c>
-      <c r="CB33">
-        <v>0</v>
-      </c>
     </row>
-    <row r="34" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>42248</v>
       </c>
@@ -7017,11 +6915,8 @@
       <c r="CA34">
         <v>1.8737786978129112E-3</v>
       </c>
-      <c r="CB34">
-        <v>0</v>
-      </c>
     </row>
-    <row r="35" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>42278</v>
       </c>
@@ -7199,11 +7094,8 @@
       <c r="CA35">
         <v>2.8962532173169464E-2</v>
       </c>
-      <c r="CB35">
-        <v>0</v>
-      </c>
     </row>
-    <row r="36" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>42309</v>
       </c>
@@ -7381,11 +7273,8 @@
       <c r="CA36">
         <v>-6.7486043190374989E-2</v>
       </c>
-      <c r="CB36">
-        <v>0</v>
-      </c>
     </row>
-    <row r="37" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>42339</v>
       </c>
@@ -7563,11 +7452,8 @@
       <c r="CA37">
         <v>-6.0609998329281822E-3</v>
       </c>
-      <c r="CB37">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="38" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>42370</v>
       </c>
@@ -7745,11 +7631,8 @@
       <c r="CA38">
         <v>2.8071158425549969E-2</v>
       </c>
-      <c r="CB38">
-        <v>0</v>
-      </c>
     </row>
-    <row r="39" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>42401</v>
       </c>
@@ -7927,11 +7810,8 @@
       <c r="CA39">
         <v>0.1008438473626363</v>
       </c>
-      <c r="CB39">
-        <v>0</v>
-      </c>
     </row>
-    <row r="40" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>42430</v>
       </c>
@@ -8109,11 +7989,8 @@
       <c r="CA40">
         <v>3.5092785886973621E-2</v>
       </c>
-      <c r="CB40">
-        <v>0</v>
-      </c>
     </row>
-    <row r="41" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>42461</v>
       </c>
@@ -8291,11 +8168,8 @@
       <c r="CA41">
         <v>-1.007604865838696E-2</v>
       </c>
-      <c r="CB41">
-        <v>0</v>
-      </c>
     </row>
-    <row r="42" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>42491</v>
       </c>
@@ -8473,11 +8347,8 @@
       <c r="CA42">
         <v>1.1684463126701017E-2</v>
       </c>
-      <c r="CB42">
-        <v>0</v>
-      </c>
     </row>
-    <row r="43" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>42522</v>
       </c>
@@ -8655,11 +8526,8 @@
       <c r="CA43">
         <v>1.9278374312481583E-2</v>
       </c>
-      <c r="CB43">
-        <v>0</v>
-      </c>
     </row>
-    <row r="44" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42552</v>
       </c>
@@ -8837,11 +8705,8 @@
       <c r="CA44">
         <v>4.3926437858732514E-2</v>
       </c>
-      <c r="CB44">
-        <v>0</v>
-      </c>
     </row>
-    <row r="45" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>42583</v>
       </c>
@@ -9019,11 +8884,8 @@
       <c r="CA45">
         <v>1.96738479952141E-3</v>
       </c>
-      <c r="CB45">
-        <v>0</v>
-      </c>
     </row>
-    <row r="46" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>42614</v>
       </c>
@@ -9201,11 +9063,8 @@
       <c r="CA46">
         <v>-1.0765773500668208E-2</v>
       </c>
-      <c r="CB46">
-        <v>0</v>
-      </c>
     </row>
-    <row r="47" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>42644</v>
       </c>
@@ -9383,11 +9242,8 @@
       <c r="CA47">
         <v>-4.7267567791941079E-2</v>
       </c>
-      <c r="CB47">
-        <v>0</v>
-      </c>
     </row>
-    <row r="48" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>42675</v>
       </c>
@@ -9565,11 +9421,8 @@
       <c r="CA48">
         <v>-2.2101110600611595E-2</v>
       </c>
-      <c r="CB48">
-        <v>0.5</v>
-      </c>
     </row>
-    <row r="49" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>42705</v>
       </c>
@@ -9747,11 +9600,8 @@
       <c r="CA49">
         <v>-6.8830600738772674E-2</v>
       </c>
-      <c r="CB49">
-        <v>0</v>
-      </c>
     </row>
-    <row r="50" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>42736</v>
       </c>
@@ -9929,11 +9779,8 @@
       <c r="CA50">
         <v>3.3396838652991256E-2</v>
       </c>
-      <c r="CB50">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="51" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>42767</v>
       </c>
@@ -10111,11 +9958,8 @@
       <c r="CA51">
         <v>3.9456183180402338E-2</v>
       </c>
-      <c r="CB51">
-        <v>0</v>
-      </c>
     </row>
-    <row r="52" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>42795</v>
       </c>
@@ -10293,11 +10137,8 @@
       <c r="CA52">
         <v>-3.684896782396696E-3</v>
       </c>
-      <c r="CB52">
-        <v>0</v>
-      </c>
     </row>
-    <row r="53" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>42826</v>
       </c>
@@ -10475,11 +10316,8 @@
       <c r="CA53">
         <v>3.5644031148900135E-2</v>
       </c>
-      <c r="CB53">
-        <v>0</v>
-      </c>
     </row>
-    <row r="54" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>42856</v>
       </c>
@@ -10657,11 +10495,8 @@
       <c r="CA54">
         <v>-2.3538738059918241E-2</v>
       </c>
-      <c r="CB54">
-        <v>0</v>
-      </c>
     </row>
-    <row r="55" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>42887</v>
       </c>
@@ -10839,11 +10674,8 @@
       <c r="CA55">
         <v>1.1968683685936732E-2</v>
       </c>
-      <c r="CB55">
-        <v>0</v>
-      </c>
     </row>
-    <row r="56" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>42917</v>
       </c>
@@ -11021,11 +10853,8 @@
       <c r="CA56">
         <v>-1.518701795912536E-2</v>
       </c>
-      <c r="CB56">
-        <v>0</v>
-      </c>
     </row>
-    <row r="57" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>42948</v>
       </c>
@@ -11203,11 +11032,8 @@
       <c r="CA57">
         <v>3.3366939549139163E-2</v>
       </c>
-      <c r="CB57">
-        <v>0</v>
-      </c>
     </row>
-    <row r="58" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>42979</v>
       </c>
@@ -11385,11 +11211,8 @@
       <c r="CA58">
         <v>2.3828850626746334E-2</v>
       </c>
-      <c r="CB58">
-        <v>0</v>
-      </c>
     </row>
-    <row r="59" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>43009</v>
       </c>
@@ -11567,11 +11390,8 @@
       <c r="CA59">
         <v>-2.6293119878025517E-2</v>
       </c>
-      <c r="CB59">
-        <v>0</v>
-      </c>
     </row>
-    <row r="60" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>43040</v>
       </c>
@@ -11749,11 +11569,8 @@
       <c r="CA60">
         <v>3.382240107730583E-3</v>
       </c>
-      <c r="CB60">
-        <v>0</v>
-      </c>
     </row>
-    <row r="61" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>43070</v>
       </c>
@@ -11931,11 +11748,8 @@
       <c r="CA61">
         <v>-8.3724777228109115E-3</v>
       </c>
-      <c r="CB61">
-        <v>0</v>
-      </c>
     </row>
-    <row r="62" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>43101</v>
       </c>
@@ -12173,11 +11987,8 @@
       <c r="CA62">
         <v>4.8912145414486519E-2</v>
       </c>
-      <c r="CB62">
-        <v>0</v>
-      </c>
     </row>
-    <row r="63" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>43132</v>
       </c>
@@ -12415,11 +12226,8 @@
       <c r="CA63">
         <v>-1.2678074433050135E-3</v>
       </c>
-      <c r="CB63">
-        <v>0</v>
-      </c>
     </row>
-    <row r="64" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>43160</v>
       </c>
@@ -12657,11 +12465,8 @@
       <c r="CA64">
         <v>-4.9800198299431164E-3</v>
       </c>
-      <c r="CB64">
-        <v>0</v>
-      </c>
     </row>
-    <row r="65" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>43191</v>
       </c>
@@ -12899,11 +12704,8 @@
       <c r="CA65">
         <v>6.4845360046501543E-3</v>
       </c>
-      <c r="CB65">
-        <v>0</v>
-      </c>
     </row>
-    <row r="66" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>43221</v>
       </c>
@@ -13141,11 +12943,8 @@
       <c r="CA66">
         <v>-2.0175807032281168E-2</v>
       </c>
-      <c r="CB66">
-        <v>0</v>
-      </c>
     </row>
-    <row r="67" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>43252</v>
       </c>
@@ -13383,11 +13182,8 @@
       <c r="CA67">
         <v>-2.1341416739386831E-2</v>
       </c>
-      <c r="CB67">
-        <v>1.25</v>
-      </c>
     </row>
-    <row r="68" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>43282</v>
       </c>
@@ -13625,11 +13421,8 @@
       <c r="CA68">
         <v>-3.2123582323034805E-2</v>
       </c>
-      <c r="CB68">
-        <v>-1</v>
-      </c>
     </row>
-    <row r="69" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>43313</v>
       </c>
@@ -13867,11 +13660,8 @@
       <c r="CA69">
         <v>-2.792077127595094E-2</v>
       </c>
-      <c r="CB69">
-        <v>0</v>
-      </c>
     </row>
-    <row r="70" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>43344</v>
       </c>
@@ -14109,11 +13899,8 @@
       <c r="CA70">
         <v>-5.1376695929769012E-3</v>
       </c>
-      <c r="CB70">
-        <v>3</v>
-      </c>
     </row>
-    <row r="71" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>43374</v>
       </c>
@@ -14351,11 +14138,8 @@
       <c r="CA71">
         <v>2.0564886771956115E-2</v>
       </c>
-      <c r="CB71">
-        <v>0</v>
-      </c>
     </row>
-    <row r="72" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>43405</v>
       </c>
@@ -14593,11 +14377,8 @@
       <c r="CA72">
         <v>9.0067222900058752E-5</v>
       </c>
-      <c r="CB72">
-        <v>0</v>
-      </c>
     </row>
-    <row r="73" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>43435</v>
       </c>
@@ -14835,11 +14616,8 @@
       <c r="CA73">
         <v>2.6632935435804139E-2</v>
       </c>
-      <c r="CB73">
-        <v>0</v>
-      </c>
     </row>
-    <row r="74" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>43466</v>
       </c>
@@ -15077,11 +14855,8 @@
       <c r="CA74">
         <v>2.6141393197495866E-2</v>
       </c>
-      <c r="CB74">
-        <v>0</v>
-      </c>
     </row>
-    <row r="75" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>43497</v>
       </c>
@@ -15319,11 +15094,8 @@
       <c r="CA75">
         <v>2.5685264196839919E-2</v>
       </c>
-      <c r="CB75">
-        <v>0</v>
-      </c>
     </row>
-    <row r="76" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>43525</v>
       </c>
@@ -15561,11 +15333,8 @@
       <c r="CA76">
         <v>-1.2123232659988825E-2</v>
       </c>
-      <c r="CB76">
-        <v>0</v>
-      </c>
     </row>
-    <row r="77" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>43556</v>
       </c>
@@ -15803,11 +15572,8 @@
       <c r="CA77">
         <v>-1.3898050284557151E-2</v>
       </c>
-      <c r="CB77">
-        <v>0</v>
-      </c>
     </row>
-    <row r="78" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>43586</v>
       </c>
@@ -16045,11 +15811,8 @@
       <c r="CA78">
         <v>-2.6678904220400756E-3</v>
       </c>
-      <c r="CB78">
-        <v>0</v>
-      </c>
     </row>
-    <row r="79" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>43617</v>
       </c>
@@ -16287,11 +16050,8 @@
       <c r="CA79">
         <v>8.0773340196376608E-2</v>
       </c>
-      <c r="CB79">
-        <v>0</v>
-      </c>
     </row>
-    <row r="80" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>43647</v>
       </c>
@@ -16529,11 +16289,8 @@
       <c r="CA80">
         <v>2.0406985134939992E-2</v>
       </c>
-      <c r="CB80">
-        <v>-1.75</v>
-      </c>
     </row>
-    <row r="81" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>43678</v>
       </c>
@@ -16771,11 +16528,8 @@
       <c r="CA81">
         <v>5.341989137813985E-2</v>
       </c>
-      <c r="CB81">
-        <v>0</v>
-      </c>
     </row>
-    <row r="82" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>43709</v>
       </c>
@@ -17013,11 +16767,8 @@
       <c r="CA82">
         <v>1.0089821565231638E-2</v>
       </c>
-      <c r="CB82">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="83" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>43739</v>
       </c>
@@ -17255,11 +17006,8 @@
       <c r="CA83">
         <v>-6.1276708869172358E-3</v>
       </c>
-      <c r="CB83">
-        <v>-1.5</v>
-      </c>
     </row>
-    <row r="84" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>43770</v>
       </c>
@@ -17497,11 +17245,8 @@
       <c r="CA84">
         <v>-1.5072587817550831E-2</v>
       </c>
-      <c r="CB84">
-        <v>0</v>
-      </c>
     </row>
-    <row r="85" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>43800</v>
       </c>
@@ -17739,11 +17484,8 @@
       <c r="CA85">
         <v>4.2705157886875345E-3</v>
       </c>
-      <c r="CB85">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="86" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>43831</v>
       </c>
@@ -17981,11 +17723,8 @@
       <c r="CA86">
         <v>5.5780905636906963E-2</v>
       </c>
-      <c r="CB86">
-        <v>0</v>
-      </c>
     </row>
-    <row r="87" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>43862</v>
       </c>
@@ -18223,11 +17962,8 @@
       <c r="CA87">
         <v>2.5683714437564342E-2</v>
       </c>
-      <c r="CB87">
-        <v>0</v>
-      </c>
     </row>
-    <row r="88" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>43891</v>
       </c>
@@ -18465,11 +18201,8 @@
       <c r="CA88">
         <v>1.2348607816206725E-2</v>
       </c>
-      <c r="CB88">
-        <v>0</v>
-      </c>
     </row>
-    <row r="89" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>43922</v>
       </c>
@@ -18707,11 +18440,8 @@
       <c r="CA89">
         <v>3.5977256749589959E-2</v>
       </c>
-      <c r="CB89">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="90" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>43952</v>
       </c>
@@ -18949,11 +18679,8 @@
       <c r="CA90">
         <v>2.6298871374827337E-2</v>
       </c>
-      <c r="CB90">
-        <v>0</v>
-      </c>
     </row>
-    <row r="91" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>43983</v>
       </c>
@@ -19191,11 +18918,8 @@
       <c r="CA91">
         <v>4.1760918740219033E-4</v>
       </c>
-      <c r="CB91">
-        <v>0.25</v>
-      </c>
     </row>
-    <row r="92" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>44013</v>
       </c>
@@ -19433,11 +19157,8 @@
       <c r="CA92">
         <v>7.0992915202745754E-2</v>
       </c>
-      <c r="CB92">
-        <v>0</v>
-      </c>
     </row>
-    <row r="93" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>44044</v>
       </c>
@@ -19675,11 +19396,8 @@
       <c r="CA93">
         <v>6.3407081801793996E-2</v>
       </c>
-      <c r="CB93">
-        <v>0</v>
-      </c>
     </row>
-    <row r="94" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>44075</v>
       </c>
@@ -19917,11 +19635,8 @@
       <c r="CA94">
         <v>-2.2062716351048728E-2</v>
       </c>
-      <c r="CB94">
-        <v>2</v>
-      </c>
     </row>
-    <row r="95" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>44105</v>
       </c>
@@ -20159,11 +19874,8 @@
       <c r="CA95">
         <v>-9.2084578305727804E-3</v>
       </c>
-      <c r="CB95">
-        <v>-1.75</v>
-      </c>
     </row>
-    <row r="96" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>44136</v>
       </c>
@@ -20401,11 +20113,8 @@
       <c r="CA96">
         <v>-1.287715998465877E-2</v>
       </c>
-      <c r="CB96">
-        <v>0</v>
-      </c>
     </row>
-    <row r="97" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>44166</v>
       </c>
@@ -20643,11 +20352,8 @@
       <c r="CA97">
         <v>-7.387458352405174E-3</v>
       </c>
-      <c r="CB97">
-        <v>0.5</v>
-      </c>
     </row>
-    <row r="98" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>44197</v>
       </c>
@@ -20885,11 +20591,8 @@
       <c r="CA98">
         <v>3.9356990423489169E-3</v>
       </c>
-      <c r="CB98">
-        <v>0</v>
-      </c>
     </row>
-    <row r="99" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>44228</v>
       </c>
@@ -21127,11 +20830,8 @@
       <c r="CA99">
         <v>-4.5526405742608134E-2</v>
       </c>
-      <c r="CB99">
-        <v>0</v>
-      </c>
     </row>
-    <row r="100" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>44256</v>
       </c>
@@ -21369,11 +21069,8 @@
       <c r="CA100">
         <v>-3.9209212794055093E-2</v>
       </c>
-      <c r="CB100">
-        <v>1</v>
-      </c>
     </row>
-    <row r="101" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>44287</v>
       </c>
@@ -21611,11 +21308,8 @@
       <c r="CA101">
         <v>2.4006849115613793E-2</v>
       </c>
-      <c r="CB101">
-        <v>0</v>
-      </c>
     </row>
-    <row r="102" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>44317</v>
       </c>
@@ -21853,11 +21547,8 @@
       <c r="CA102">
         <v>5.9372209551651345E-2</v>
       </c>
-      <c r="CB102">
-        <v>0</v>
-      </c>
     </row>
-    <row r="103" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>44348</v>
       </c>
@@ -22095,11 +21786,8 @@
       <c r="CA103">
         <v>-1.5982862849104995E-2</v>
       </c>
-      <c r="CB103">
-        <v>0</v>
-      </c>
     </row>
-    <row r="104" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>44378</v>
       </c>
@@ -22337,11 +22025,8 @@
       <c r="CA104">
         <v>-1.2166843986141762E-2</v>
       </c>
-      <c r="CB104">
-        <v>0</v>
-      </c>
     </row>
-    <row r="105" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>44409</v>
       </c>
@@ -22579,11 +22264,8 @@
       <c r="CA105">
         <v>-1.7663141034492291E-2</v>
       </c>
-      <c r="CB105">
-        <v>0</v>
-      </c>
     </row>
-    <row r="106" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>44440</v>
       </c>
@@ -22821,11 +22503,8 @@
       <c r="CA106">
         <v>9.5020156642688924E-4</v>
       </c>
-      <c r="CB106">
-        <v>-1</v>
-      </c>
     </row>
-    <row r="107" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>44470</v>
       </c>
@@ -23063,11 +22742,8 @@
       <c r="CA107">
         <v>-1.381820632941233E-3</v>
       </c>
-      <c r="CB107">
-        <v>-1</v>
-      </c>
     </row>
-    <row r="108" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>44501</v>
       </c>
@@ -23305,11 +22981,8 @@
       <c r="CA108">
         <v>2.9964000449994366E-2</v>
       </c>
-      <c r="CB108">
-        <v>0</v>
-      </c>
     </row>
-    <row r="109" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>44531</v>
       </c>
@@ -23547,11 +23220,8 @@
       <c r="CA109">
         <v>-2.0676435089865386E-2</v>
       </c>
-      <c r="CB109">
-        <v>0</v>
-      </c>
     </row>
-    <row r="110" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>44562</v>
       </c>
@@ -23789,11 +23459,8 @@
       <c r="CA110">
         <v>1.0417073293144785E-2</v>
       </c>
-      <c r="CB110">
-        <v>0</v>
-      </c>
     </row>
-    <row r="111" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>44593</v>
       </c>
@@ -24031,11 +23698,8 @@
       <c r="CA111">
         <v>2.2998084872701829E-2</v>
       </c>
-      <c r="CB111">
-        <v>0</v>
-      </c>
     </row>
-    <row r="112" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>44621</v>
       </c>
@@ -24273,11 +23937,8 @@
       <c r="CA112">
         <v>5.3863915923951788E-2</v>
       </c>
-      <c r="CB112">
-        <v>0</v>
-      </c>
     </row>
-    <row r="113" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>44652</v>
       </c>
@@ -24515,11 +24176,8 @@
       <c r="CA113">
         <v>-4.8633152452134398E-3</v>
       </c>
-      <c r="CB113">
-        <v>0</v>
-      </c>
     </row>
-    <row r="114" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>44682</v>
       </c>
@@ -24757,11 +24415,8 @@
       <c r="CA114">
         <v>-5.0892535624260549E-2</v>
       </c>
-      <c r="CB114">
-        <v>0</v>
-      </c>
     </row>
-    <row r="115" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>44713</v>
       </c>
@@ -24999,11 +24654,8 @@
       <c r="CA115">
         <v>-4.2548117313561118E-3</v>
       </c>
-      <c r="CB115">
-        <v>0</v>
-      </c>
     </row>
-    <row r="116" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>44743</v>
       </c>
@@ -25241,11 +24893,8 @@
       <c r="CA116">
         <v>-4.995863090053998E-2</v>
       </c>
-      <c r="CB116">
-        <v>0</v>
-      </c>
     </row>
-    <row r="117" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>44774</v>
       </c>
@@ -25483,11 +25132,8 @@
       <c r="CA117">
         <v>1.231278719332618E-2</v>
       </c>
-      <c r="CB117">
-        <v>-1</v>
-      </c>
     </row>
-    <row r="118" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>44805</v>
       </c>
@@ -25725,11 +25371,8 @@
       <c r="CA118">
         <v>-4.848231012604487E-2</v>
       </c>
-      <c r="CB118">
-        <v>-1</v>
-      </c>
     </row>
-    <row r="119" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>44835</v>
       </c>
@@ -25967,11 +25610,8 @@
       <c r="CA119">
         <v>-1.3080176305787061E-2</v>
       </c>
-      <c r="CB119">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="120" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>44866</v>
       </c>
@@ -26209,11 +25849,8 @@
       <c r="CA120">
         <v>4.1797755517785751E-2</v>
       </c>
-      <c r="CB120">
-        <v>0</v>
-      </c>
     </row>
-    <row r="121" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>44896</v>
       </c>
@@ -26451,11 +26088,8 @@
       <c r="CA121">
         <v>3.7604207042978732E-2</v>
       </c>
-      <c r="CB121">
-        <v>0</v>
-      </c>
     </row>
-    <row r="122" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>44927</v>
       </c>
@@ -26693,11 +26327,8 @@
       <c r="CA122">
         <v>6.0378136970109297E-2</v>
       </c>
-      <c r="CB122">
-        <v>0</v>
-      </c>
     </row>
-    <row r="123" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>44958</v>
       </c>
@@ -26935,11 +26566,8 @@
       <c r="CA123">
         <v>-2.9887160719731631E-2</v>
       </c>
-      <c r="CB123">
-        <v>0.5</v>
-      </c>
     </row>
-    <row r="124" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>44986</v>
       </c>
@@ -27177,11 +26805,8 @@
       <c r="CA124">
         <v>4.4780973235482247E-2</v>
       </c>
-      <c r="CB124">
-        <v>0</v>
-      </c>
     </row>
-    <row r="125" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>45017</v>
       </c>
@@ -27419,11 +27044,8 @@
       <c r="CA125">
         <v>3.463892923843126E-2</v>
       </c>
-      <c r="CB125">
-        <v>0</v>
-      </c>
     </row>
-    <row r="126" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>45047</v>
       </c>
@@ -27661,11 +27283,8 @@
       <c r="CA126">
         <v>-6.0720929416306912E-3</v>
       </c>
-      <c r="CB126">
-        <v>0</v>
-      </c>
     </row>
-    <row r="127" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>45078</v>
       </c>
@@ -27903,11 +27522,8 @@
       <c r="CA127">
         <v>-1.4508692098917364E-2</v>
       </c>
-      <c r="CB127">
-        <v>-5</v>
-      </c>
     </row>
-    <row r="128" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>45108</v>
       </c>
@@ -28145,11 +27761,8 @@
       <c r="CA128">
         <v>-2.963910929101643E-3</v>
       </c>
-      <c r="CB128">
-        <v>-1</v>
-      </c>
     </row>
-    <row r="129" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>45139</v>
       </c>
@@ -28387,11 +28000,8 @@
       <c r="CA129">
         <v>-1.5839113625745194E-2</v>
       </c>
-      <c r="CB129">
-        <v>5</v>
-      </c>
     </row>
-    <row r="130" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>45170</v>
       </c>
@@ -28629,11 +28239,8 @@
       <c r="CA130">
         <v>1.0016380956356929E-3</v>
       </c>
-      <c r="CB130">
-        <v>0</v>
-      </c>
     </row>
-    <row r="131" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>45200</v>
       </c>
@@ -28871,11 +28478,8 @@
       <c r="CA131">
         <v>3.267701351900687E-3</v>
       </c>
-      <c r="CB131">
-        <v>0</v>
-      </c>
     </row>
-    <row r="132" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>45231</v>
       </c>
@@ -29113,11 +28717,8 @@
       <c r="CA132">
         <v>2.8284979610919248E-2</v>
       </c>
-      <c r="CB132">
-        <v>2.5</v>
-      </c>
     </row>
-    <row r="133" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>45261</v>
       </c>
@@ -29355,11 +28956,8 @@
       <c r="CA133">
         <v>3.20080828492042E-2</v>
       </c>
-      <c r="CB133">
-        <v>0</v>
-      </c>
     </row>
-    <row r="134" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>45292</v>
       </c>
@@ -29597,11 +29195,8 @@
       <c r="CA134">
         <v>-1.5223754931811273E-3</v>
       </c>
-      <c r="CB134">
-        <v>0</v>
-      </c>
     </row>
-    <row r="135" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>45323</v>
       </c>
@@ -29839,11 +29434,8 @@
       <c r="CA135">
         <v>-9.3148670180168702E-3</v>
       </c>
-      <c r="CB135">
-        <v>0</v>
-      </c>
     </row>
-    <row r="136" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>45352</v>
       </c>
@@ -30081,11 +29673,8 @@
       <c r="CA136">
         <v>6.8459730298156662E-2</v>
       </c>
-      <c r="CB136">
-        <v>5</v>
-      </c>
     </row>
-    <row r="137" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>45383</v>
       </c>
@@ -30323,11 +29912,8 @@
       <c r="CA137">
         <v>8.3998351157200224E-2</v>
       </c>
-      <c r="CB137">
-        <v>0</v>
-      </c>
     </row>
-    <row r="138" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>45413</v>
       </c>
@@ -30565,11 +30151,8 @@
       <c r="CA138">
         <v>4.9734025507917057E-3</v>
       </c>
-      <c r="CB138">
-        <v>0</v>
-      </c>
     </row>
-    <row r="139" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>45444</v>
       </c>
@@ -30807,11 +30390,8 @@
       <c r="CA139">
         <v>-8.996254395027492E-3</v>
       </c>
-      <c r="CB139">
-        <v>0</v>
-      </c>
     </row>
-    <row r="140" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>45474</v>
       </c>
@@ -31049,11 +30629,8 @@
       <c r="CA140">
         <v>3.0901828883750371E-2</v>
       </c>
-      <c r="CB140">
-        <v>0</v>
-      </c>
     </row>
-    <row r="141" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>45505</v>
       </c>
@@ -31291,11 +30868,8 @@
       <c r="CA141">
         <v>3.3084196158071677E-2</v>
       </c>
-      <c r="CB141">
-        <v>0</v>
-      </c>
     </row>
-    <row r="142" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>45536</v>
       </c>
@@ -31533,11 +31107,8 @@
       <c r="CA142">
         <v>4.220410399361918E-2</v>
       </c>
-      <c r="CB142">
-        <v>0</v>
-      </c>
     </row>
-    <row r="143" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>45566</v>
       </c>
@@ -31775,11 +31346,8 @@
       <c r="CA143">
         <v>3.8060010126660382E-2</v>
       </c>
-      <c r="CB143">
-        <v>0</v>
-      </c>
     </row>
-    <row r="144" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>45597</v>
       </c>
@@ -32017,11 +31585,8 @@
       <c r="CA144">
         <v>-5.6037532114531219E-3</v>
       </c>
-      <c r="CB144">
-        <v>0</v>
-      </c>
     </row>
-    <row r="145" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>45627</v>
       </c>
@@ -32259,11 +31824,8 @@
       <c r="CA145">
         <v>-1.4404732930185626E-2</v>
       </c>
-      <c r="CB145">
-        <v>-0.75</v>
-      </c>
     </row>
-    <row r="146" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>45658</v>
       </c>
@@ -32501,11 +32063,8 @@
       <c r="CA146">
         <v>3.6274114992135731E-2</v>
       </c>
-      <c r="CB146">
-        <v>0</v>
-      </c>
     </row>
-    <row r="147" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>45689</v>
       </c>
@@ -32743,11 +32302,8 @@
       <c r="CA147">
         <v>5.9937822162586363E-2</v>
       </c>
-      <c r="CB147">
-        <v>0</v>
-      </c>
     </row>
-    <row r="148" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>45717</v>
       </c>
@@ -32985,11 +32541,8 @@
       <c r="CA148">
         <v>3.7172059561074278E-2</v>
       </c>
-      <c r="CB148">
-        <v>0</v>
-      </c>
     </row>
-    <row r="149" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>45748</v>
       </c>
@@ -33227,11 +32780,8 @@
       <c r="CA149">
         <v>7.8152616870426961E-2</v>
       </c>
-      <c r="CB149">
-        <v>3.5</v>
-      </c>
     </row>
-    <row r="150" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>45778</v>
       </c>
@@ -33469,11 +33019,8 @@
       <c r="CA150">
         <v>1.3148900237243133E-2</v>
       </c>
-      <c r="CB150">
-        <v>0</v>
-      </c>
     </row>
-    <row r="151" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>45809</v>
       </c>
@@ -33708,11 +33255,8 @@
       <c r="CA151">
         <v>2.6560992587346011E-2</v>
       </c>
-      <c r="CB151">
-        <v>0</v>
-      </c>
     </row>
-    <row r="152" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>45839</v>
       </c>
@@ -33947,11 +33491,8 @@
       <c r="CA152">
         <v>-5.0052342318764875E-3</v>
       </c>
-      <c r="CB152">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="153" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>45870</v>
       </c>
@@ -34186,11 +33727,8 @@
       <c r="CA153">
         <v>6.6743383199079354E-3</v>
       </c>
-      <c r="CB153">
-        <v>0</v>
-      </c>
     </row>
-    <row r="154" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>45901</v>
       </c>
@@ -34425,11 +33963,8 @@
       <c r="CA154">
         <v>8.9572978461867292E-2</v>
       </c>
-      <c r="CB154">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="155" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>45931</v>
       </c>
@@ -34661,11 +34196,8 @@
       <c r="CA155">
         <v>0.10096575704561195</v>
       </c>
-      <c r="CB155">
-        <v>0.10000000000000142</v>
-      </c>
     </row>
-    <row r="156" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>45962</v>
       </c>
@@ -34897,11 +34429,8 @@
       <c r="CA156">
         <v>1.042035359898219E-2</v>
       </c>
-      <c r="CB156">
-        <v>-0.5</v>
-      </c>
     </row>
-    <row r="157" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>45992</v>
       </c>
@@ -35133,11 +34662,8 @@
       <c r="CA157">
         <v>6.4170179826420037E-2</v>
       </c>
-      <c r="CB157">
-        <v>0</v>
-      </c>
     </row>
-    <row r="158" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>46023</v>
       </c>
@@ -35312,11 +34838,8 @@
       <c r="CA158">
         <v>7.6644192411543521E-2</v>
       </c>
-      <c r="CB158">
-        <v>0.5</v>
-      </c>
     </row>
-    <row r="159" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>46054</v>
       </c>
@@ -35491,11 +35014,8 @@
       <c r="CA159">
         <v>8.0693749879735543E-2</v>
       </c>
-      <c r="CB159">
-        <v>0</v>
-      </c>
     </row>
-    <row r="160" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>46082</v>
       </c>
@@ -35670,11 +35190,8 @@
       <c r="CA160">
         <v>-4.6581239699996613E-2</v>
       </c>
-      <c r="CB160">
-        <v>0</v>
-      </c>
     </row>
-    <row r="161" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:79" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>46113</v>
       </c>
@@ -35725,9 +35242,6 @@
       </c>
       <c r="CA161">
         <v>-2.0302293345728306E-2</v>
-      </c>
-      <c r="CB161">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -35746,21 +35260,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" t="s">
         <v>81</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>82</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>83</v>
-      </c>
-      <c r="D1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" s="2">
         <v>390227835.36000001</v>
@@ -35775,7 +35289,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="2">
         <v>401221933.49000001</v>
@@ -35790,7 +35304,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2">
         <v>413147128.95999998</v>
@@ -35805,7 +35319,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="2">
         <v>420899357.13999999</v>
@@ -35820,7 +35334,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2">
         <v>427422971.16000003</v>
@@ -35835,7 +35349,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="2">
         <v>433744307.63</v>
@@ -35850,7 +35364,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="2">
         <v>444925181.74000001</v>
@@ -35865,7 +35379,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="2">
         <v>451332544.89999998</v>
@@ -35880,7 +35394,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="2">
         <v>471414690.88</v>
@@ -35895,7 +35409,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2">
         <v>487717715.62</v>
@@ -35910,7 +35424,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2">
         <v>504797488.74000001</v>
@@ -35925,7 +35439,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="2">
         <v>527155061.61000001</v>
@@ -35940,7 +35454,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2">
         <v>544392185.99000001</v>
@@ -35955,7 +35469,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" s="2">
         <v>558204485.26999998</v>
@@ -35970,7 +35484,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="2">
         <v>574553273.33000004</v>
@@ -35985,7 +35499,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2">
         <v>580341918.22000003</v>
@@ -36000,7 +35514,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B18" s="2">
         <v>567978011.59000003</v>
@@ -36015,7 +35529,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="2">
         <v>572143739.09000003</v>
@@ -36030,7 +35544,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B20" s="2">
         <v>576684317.36000001</v>
@@ -36045,7 +35559,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B21" s="2">
         <v>605870804.00999999</v>
@@ -36060,7 +35574,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B22" s="2">
         <v>654025953.48000002</v>
@@ -36075,7 +35589,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B23" s="2">
         <v>696534265.83000004</v>
@@ -36090,7 +35604,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B24" s="2">
         <v>774599766.38999999</v>
@@ -36105,7 +35619,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B25" s="2">
         <v>880424670.61000001</v>
@@ -36120,7 +35634,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="2">
         <v>909873259.83000004</v>
@@ -36135,7 +35649,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="2">
         <v>944080753.33000004</v>
@@ -36150,7 +35664,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28" s="2">
         <v>974793555.98000002</v>
@@ -36165,7 +35679,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2">
         <v>1027495756.51</v>
@@ -36180,7 +35694,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2">
         <v>1086253551.95</v>
@@ -36195,7 +35709,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" s="2">
         <v>1150178205.1300001</v>
@@ -36210,7 +35724,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" s="2">
         <v>1330347655.3800001</v>
@@ -36225,7 +35739,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2">
         <v>1457377161.0999999</v>
@@ -36240,7 +35754,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B34" s="2">
         <v>1688919834.6600001</v>
@@ -36255,7 +35769,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B35" s="2">
         <v>2037281492.1900001</v>
@@ -36270,7 +35784,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36" s="2">
         <v>2436758221.5</v>
@@ -36285,7 +35799,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B37" s="2">
         <v>2665818012.1599998</v>
@@ -36300,7 +35814,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B38" s="2">
         <v>2990367254.1399999</v>
@@ -36315,7 +35829,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2">
         <v>3390429733.4699998</v>
@@ -36330,7 +35844,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B40" s="2">
         <v>3633815862.79</v>
@@ -36345,7 +35859,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B41" s="2">
         <v>3943449846.71</v>
@@ -36360,7 +35874,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="2">
         <v>4408951905.1199999</v>
@@ -36375,7 +35889,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43" s="2">
         <v>4786752209.4399996</v>
@@ -36390,7 +35904,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B44" s="2">
         <v>5346126597.1599998</v>
@@ -36405,7 +35919,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B45" s="2">
         <v>5906584627.25</v>
